--- a/PicoComputer3BOM.xlsx
+++ b/PicoComputer3BOM.xlsx
@@ -535,148 +535,148 @@
     <t>30</t>
   </si>
   <si>
+    <t>2.2Ω</t>
+  </si>
+  <si>
+    <t>R29</t>
+  </si>
+  <si>
+    <t>R0805</t>
+  </si>
+  <si>
+    <t>C17521</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>5.1KΩ</t>
+  </si>
+  <si>
+    <t>R31,R32</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>5.1kΩ</t>
+  </si>
+  <si>
+    <t>C25905</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>1MΩ</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>0402WGF1004TCE</t>
+  </si>
+  <si>
+    <t>C26083</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
     <t>10kΩ</t>
   </si>
   <si>
-    <t>R23,R75,R91,R92,R93</t>
-  </si>
-  <si>
-    <t>R0402</t>
-  </si>
-  <si>
-    <t>0402WGF1002TCE</t>
-  </si>
-  <si>
-    <t>C25744</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>2.2Ω</t>
-  </si>
-  <si>
-    <t>R29</t>
-  </si>
-  <si>
-    <t>R0805</t>
-  </si>
-  <si>
-    <t>C17521</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>5.1KΩ</t>
-  </si>
-  <si>
-    <t>R31,R32</t>
-  </si>
-  <si>
-    <t>5.1kΩ</t>
-  </si>
-  <si>
-    <t>C25905</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>1MΩ</t>
-  </si>
-  <si>
-    <t>R33</t>
-  </si>
-  <si>
-    <t>0402WGF1004TCE</t>
-  </si>
-  <si>
-    <t>C26083</t>
+    <t>R52,R53,R94,R95,R97,R98,R99,R100</t>
+  </si>
+  <si>
+    <t>0805W8F1002T5E</t>
+  </si>
+  <si>
+    <t>C17414</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>R52,R53,R94,R95</t>
-  </si>
-  <si>
-    <t>0805W8F1002T5E</t>
-  </si>
-  <si>
-    <t>C17414</t>
+    <t>220Ω</t>
+  </si>
+  <si>
+    <t>R57,R58</t>
+  </si>
+  <si>
+    <t>0805W8F2200T5E</t>
+  </si>
+  <si>
+    <t>C17557</t>
   </si>
   <si>
     <t>35</t>
   </si>
   <si>
-    <t>220Ω</t>
-  </si>
-  <si>
-    <t>R57,R58</t>
-  </si>
-  <si>
-    <t>0805W8F2200T5E</t>
-  </si>
-  <si>
-    <t>C17557</t>
+    <t>470Ω</t>
+  </si>
+  <si>
+    <t>R59,R69,R70</t>
+  </si>
+  <si>
+    <t>0603WAF4700T5E</t>
+  </si>
+  <si>
+    <t>C23179</t>
   </si>
   <si>
     <t>36</t>
   </si>
   <si>
-    <t>470Ω</t>
-  </si>
-  <si>
-    <t>R59,R69,R70</t>
-  </si>
-  <si>
-    <t>0603WAF4700T5E</t>
-  </si>
-  <si>
-    <t>C23179</t>
+    <t>R60,R61,R62,R63,R64,R65,R66,R67,R68</t>
+  </si>
+  <si>
+    <t>0603WAF2200T5E</t>
+  </si>
+  <si>
+    <t>C22962</t>
   </si>
   <si>
     <t>37</t>
   </si>
   <si>
-    <t>R60,R61,R62,R63,R64,R65,R66,R67,R68</t>
-  </si>
-  <si>
-    <t>0603WAF2200T5E</t>
-  </si>
-  <si>
-    <t>C22962</t>
+    <t>10Ω</t>
+  </si>
+  <si>
+    <t>R79,R88</t>
+  </si>
+  <si>
+    <t>R0805_NEW</t>
+  </si>
+  <si>
+    <t>0805W8F100JT5E</t>
+  </si>
+  <si>
+    <t>C17415</t>
   </si>
   <si>
     <t>38</t>
   </si>
   <si>
-    <t>10Ω</t>
-  </si>
-  <si>
-    <t>R79,R88</t>
-  </si>
-  <si>
-    <t>R0805_NEW</t>
-  </si>
-  <si>
-    <t>0805W8F100JT5E</t>
-  </si>
-  <si>
-    <t>C17415</t>
+    <t>R90</t>
+  </si>
+  <si>
+    <t>0402WGF4700TCE</t>
+  </si>
+  <si>
+    <t>C25117</t>
   </si>
   <si>
     <t>39</t>
   </si>
   <si>
-    <t>R90</t>
-  </si>
-  <si>
-    <t>0402WGF4700TCE</t>
-  </si>
-  <si>
-    <t>C25117</t>
+    <t>R96</t>
+  </si>
+  <si>
+    <t>0603WAF1002T5E</t>
+  </si>
+  <si>
+    <t>C25804</t>
   </si>
   <si>
     <t>40</t>
@@ -2378,7 +2378,7 @@
         <v>173</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
         <v>174</v>
@@ -2390,16 +2390,16 @@
         <v>176</v>
       </c>
       <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
         <v>174</v>
-      </c>
-      <c r="G31" t="s">
-        <v>177</v>
       </c>
       <c r="H31" t="s">
         <v>171</v>
       </c>
       <c r="I31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J31" t="s">
         <v>17</v>
@@ -2407,25 +2407,25 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
         <v>179</v>
       </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>180</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>181</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>182</v>
       </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
       <c r="G32" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H32" t="s">
         <v>171</v>
@@ -2442,7 +2442,7 @@
         <v>184</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
         <v>185</v>
@@ -2451,13 +2451,13 @@
         <v>186</v>
       </c>
       <c r="E33" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s">
+        <v>185</v>
+      </c>
+      <c r="G33" t="s">
         <v>187</v>
-      </c>
-      <c r="G33" t="s">
-        <v>185</v>
       </c>
       <c r="H33" t="s">
         <v>171</v>
@@ -2474,7 +2474,7 @@
         <v>189</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C34" t="s">
         <v>190</v>
@@ -2506,28 +2506,28 @@
         <v>194</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D35" t="s">
+        <v>196</v>
+      </c>
+      <c r="E35" t="s">
+        <v>176</v>
+      </c>
+      <c r="F35" t="s">
         <v>195</v>
       </c>
-      <c r="E35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F35" t="s">
-        <v>174</v>
-      </c>
       <c r="G35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H35" t="s">
         <v>171</v>
       </c>
       <c r="I35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J35" t="s">
         <v>17</v>
@@ -2535,31 +2535,31 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D36" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" t="s">
+        <v>169</v>
+      </c>
+      <c r="F36" t="s">
         <v>200</v>
       </c>
-      <c r="E36" t="s">
-        <v>182</v>
-      </c>
-      <c r="F36" t="s">
-        <v>199</v>
-      </c>
       <c r="G36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H36" t="s">
         <v>171</v>
       </c>
       <c r="I36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J36" t="s">
         <v>17</v>
@@ -2567,13 +2567,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D37" t="s">
         <v>205</v>
@@ -2582,7 +2582,7 @@
         <v>169</v>
       </c>
       <c r="F37" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G37" t="s">
         <v>206</v>
@@ -2602,28 +2602,28 @@
         <v>208</v>
       </c>
       <c r="B38">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D38" t="s">
+        <v>210</v>
+      </c>
+      <c r="E38" t="s">
+        <v>211</v>
+      </c>
+      <c r="F38" t="s">
         <v>209</v>
       </c>
-      <c r="E38" t="s">
-        <v>169</v>
-      </c>
-      <c r="F38" t="s">
-        <v>199</v>
-      </c>
       <c r="G38" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H38" t="s">
         <v>171</v>
       </c>
       <c r="I38" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J38" t="s">
         <v>17</v>
@@ -2631,22 +2631,22 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="D39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E39" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="F39" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="G39" t="s">
         <v>216</v>
@@ -2669,16 +2669,16 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D40" t="s">
         <v>219</v>
       </c>
       <c r="E40" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F40" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="G40" t="s">
         <v>220</v>
